--- a/data/wfa_window_results_2024-10-21_2026-04-20.xlsx
+++ b/data/wfa_window_results_2024-10-21_2026-04-20.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="7c49fc85-4e29-4350-aa8a-083bb04" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="c4b404bc-8468-4ec3-9a46-309631a" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -743,16 +743,16 @@
         <v>45859</v>
       </c>
       <c r="L4" s="0" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N4" s="0" t="n">
-        <v>50</v>
+        <v>22.2222222222222</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>50</v>
+        <v>22.2222222222222</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -884,16 +884,16 @@
         <v>45859</v>
       </c>
       <c r="L7" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M7" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N7" s="0" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1025,16 +1025,16 @@
         <v>45951</v>
       </c>
       <c r="L10" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M10" s="0" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N10" s="0" t="n">
-        <v>75</v>
+        <v>42.8571428571429</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>75</v>
+        <v>42.8571428571429</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1166,16 +1166,16 @@
         <v>45951</v>
       </c>
       <c r="L13" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M13" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="0" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1307,16 +1307,16 @@
         <v>46043</v>
       </c>
       <c r="L16" s="0" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M16" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N16" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O16" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1448,16 +1448,16 @@
         <v>46043</v>
       </c>
       <c r="L19" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M19" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1589,16 +1589,16 @@
         <v>46133</v>
       </c>
       <c r="L22" s="0" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M22" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N22" s="0" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="O22" s="0" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1730,16 +1730,16 @@
         <v>46133</v>
       </c>
       <c r="L25" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M25" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N25" s="0" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="O25" s="0" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1871,16 +1871,16 @@
         <v>45859</v>
       </c>
       <c r="L28" s="0" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M28" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N28" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O28" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2012,16 +2012,16 @@
         <v>45859</v>
       </c>
       <c r="L31" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M31" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N31" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="O31" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2153,16 +2153,16 @@
         <v>45951</v>
       </c>
       <c r="L34" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M34" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N34" s="0" t="n">
-        <v>40</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O34" s="0" t="n">
-        <v>40</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2294,16 +2294,16 @@
         <v>45951</v>
       </c>
       <c r="L37" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M37" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N37" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O37" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2435,16 +2435,16 @@
         <v>46043</v>
       </c>
       <c r="L40" s="0" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M40" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N40" s="0" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="O40" s="0" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2576,16 +2576,16 @@
         <v>46043</v>
       </c>
       <c r="L43" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M43" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O43" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2717,16 +2717,16 @@
         <v>46133</v>
       </c>
       <c r="L46" s="0" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M46" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N46" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>0</v>
       </c>
       <c r="O46" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2858,16 +2858,16 @@
         <v>46133</v>
       </c>
       <c r="L49" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M49" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N49" s="0" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="O49" s="0" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2999,16 +2999,16 @@
         <v>45859</v>
       </c>
       <c r="L52" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M52" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N52" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
       <c r="O52" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3140,16 +3140,16 @@
         <v>45859</v>
       </c>
       <c r="L55" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N55" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O55" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3284,13 +3284,13 @@
         <v>3</v>
       </c>
       <c r="M58" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N58" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
       <c r="O58" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3422,16 +3422,16 @@
         <v>45951</v>
       </c>
       <c r="L61" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M61" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N61" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
       <c r="O61" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3563,16 +3563,16 @@
         <v>46043</v>
       </c>
       <c r="L64" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M64" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N64" s="0" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O64" s="0" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3704,16 +3704,16 @@
         <v>46043</v>
       </c>
       <c r="L67" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M67" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N67" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O67" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3845,16 +3845,16 @@
         <v>46133</v>
       </c>
       <c r="L70" s="0" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M70" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N70" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>25</v>
       </c>
       <c r="O70" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3986,16 +3986,16 @@
         <v>46133</v>
       </c>
       <c r="L73" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M73" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N73" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O73" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4127,16 +4127,16 @@
         <v>45859</v>
       </c>
       <c r="L76" s="0" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M76" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N76" s="0" t="n">
-        <v>28.5714285714286</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="O76" s="0" t="n">
-        <v>28.5714285714286</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4268,16 +4268,16 @@
         <v>45859</v>
       </c>
       <c r="L79" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M79" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N79" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O79" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4409,10 +4409,10 @@
         <v>45951</v>
       </c>
       <c r="L82" s="0" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M82" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N82" s="0" t="n">
         <v>50</v>
@@ -4553,13 +4553,13 @@
         <v>3</v>
       </c>
       <c r="M85" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N85" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="O85" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4691,16 +4691,16 @@
         <v>46043</v>
       </c>
       <c r="L88" s="0" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M88" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N88" s="0" t="n">
-        <v>50</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="O88" s="0" t="n">
-        <v>50</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4832,16 +4832,16 @@
         <v>46043</v>
       </c>
       <c r="L91" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M91" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N91" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
       <c r="O91" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4973,16 +4973,16 @@
         <v>46133</v>
       </c>
       <c r="L94" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M94" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N94" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>60</v>
       </c>
       <c r="O94" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>60</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5114,16 +5114,16 @@
         <v>46133</v>
       </c>
       <c r="L97" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M97" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N97" s="0" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O97" s="0" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5255,16 +5255,16 @@
         <v>45859</v>
       </c>
       <c r="L100" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M100" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N100" s="0" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="O100" s="0" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5537,16 +5537,16 @@
         <v>45951</v>
       </c>
       <c r="L106" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M106" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N106" s="0" t="n">
-        <v>60</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O106" s="0" t="n">
-        <v>60</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5678,16 +5678,16 @@
         <v>45951</v>
       </c>
       <c r="L109" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M109" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N109" s="0" t="n">
-        <v>83.3333333333333</v>
+        <v>100</v>
       </c>
       <c r="O109" s="0" t="n">
-        <v>83.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5819,16 +5819,16 @@
         <v>46043</v>
       </c>
       <c r="L112" s="0" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M112" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N112" s="0" t="n">
-        <v>71.4285714285714</v>
+        <v>50</v>
       </c>
       <c r="O112" s="0" t="n">
-        <v>71.4285714285714</v>
+        <v>50</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5960,16 +5960,16 @@
         <v>46043</v>
       </c>
       <c r="L115" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M115" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N115" s="0" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="O115" s="0" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6101,16 +6101,16 @@
         <v>46133</v>
       </c>
       <c r="L118" s="0" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M118" s="0" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N118" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="O118" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6242,16 +6242,16 @@
         <v>46133</v>
       </c>
       <c r="L121" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M121" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N121" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O121" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6383,16 +6383,16 @@
         <v>45859</v>
       </c>
       <c r="L124" s="0" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M124" s="0" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N124" s="0" t="n">
-        <v>75</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="O124" s="0" t="n">
-        <v>75</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6665,16 +6665,16 @@
         <v>45951</v>
       </c>
       <c r="L130" s="0" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M130" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N130" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="O130" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6806,7 +6806,7 @@
         <v>45951</v>
       </c>
       <c r="L133" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M133" s="0" t="n">
         <v>0</v>
@@ -6947,16 +6947,16 @@
         <v>46043</v>
       </c>
       <c r="L136" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M136" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N136" s="0" t="n">
-        <v>16.6666666666667</v>
+        <v>20</v>
       </c>
       <c r="O136" s="0" t="n">
-        <v>16.6666666666667</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7088,16 +7088,16 @@
         <v>46043</v>
       </c>
       <c r="L139" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M139" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N139" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="O139" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7229,16 +7229,16 @@
         <v>46133</v>
       </c>
       <c r="L142" s="0" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M142" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N142" s="0" t="n">
-        <v>11.1111111111111</v>
+        <v>0</v>
       </c>
       <c r="O142" s="0" t="n">
-        <v>11.1111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7370,16 +7370,16 @@
         <v>46133</v>
       </c>
       <c r="L145" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M145" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N145" s="0" t="n">
-        <v>100</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O145" s="0" t="n">
-        <v>100</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7511,16 +7511,16 @@
         <v>45859</v>
       </c>
       <c r="L148" s="0" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M148" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N148" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O148" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7652,16 +7652,16 @@
         <v>45859</v>
       </c>
       <c r="L151" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M151" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N151" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O151" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7793,16 +7793,16 @@
         <v>45951</v>
       </c>
       <c r="L154" s="0" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M154" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N154" s="0" t="n">
-        <v>44.4444444444444</v>
+        <v>100</v>
       </c>
       <c r="O154" s="0" t="n">
-        <v>44.4444444444444</v>
+        <v>100</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7934,16 +7934,16 @@
         <v>45951</v>
       </c>
       <c r="L157" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M157" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N157" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O157" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8075,16 +8075,16 @@
         <v>46043</v>
       </c>
       <c r="L160" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M160" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N160" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O160" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8216,16 +8216,16 @@
         <v>46043</v>
       </c>
       <c r="L163" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M163" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N163" s="0" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O163" s="0" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8357,16 +8357,16 @@
         <v>46133</v>
       </c>
       <c r="L166" s="0" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M166" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N166" s="0" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O166" s="0" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8501,13 +8501,13 @@
         <v>4</v>
       </c>
       <c r="M169" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N169" s="0" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="O169" s="0" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8639,16 +8639,16 @@
         <v>45859</v>
       </c>
       <c r="L172" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M172" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N172" s="0" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="O172" s="0" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8780,16 +8780,16 @@
         <v>45859</v>
       </c>
       <c r="L175" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M175" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N175" s="0" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="O175" s="0" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8921,16 +8921,16 @@
         <v>45951</v>
       </c>
       <c r="L178" s="0" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M178" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N178" s="0" t="n">
-        <v>28.5714285714286</v>
+        <v>100</v>
       </c>
       <c r="O178" s="0" t="n">
-        <v>28.5714285714286</v>
+        <v>100</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9062,16 +9062,16 @@
         <v>45951</v>
       </c>
       <c r="L181" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M181" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N181" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O181" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9203,16 +9203,16 @@
         <v>46043</v>
       </c>
       <c r="L184" s="0" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M184" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N184" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>100</v>
       </c>
       <c r="O184" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>100</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9485,16 +9485,16 @@
         <v>46133</v>
       </c>
       <c r="L190" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M190" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N190" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O190" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9626,16 +9626,16 @@
         <v>46133</v>
       </c>
       <c r="L193" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M193" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N193" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="O193" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9767,16 +9767,16 @@
         <v>45859</v>
       </c>
       <c r="L196" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M196" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N196" s="0" t="n">
-        <v>28.5714285714286</v>
+        <v>50</v>
       </c>
       <c r="O196" s="0" t="n">
-        <v>28.5714285714286</v>
+        <v>50</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9908,16 +9908,16 @@
         <v>45859</v>
       </c>
       <c r="L199" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M199" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N199" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O199" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10049,10 +10049,10 @@
         <v>45951</v>
       </c>
       <c r="L202" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M202" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N202" s="0" t="n">
         <v>100</v>
@@ -10190,10 +10190,10 @@
         <v>45951</v>
       </c>
       <c r="L205" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M205" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N205" s="0" t="n">
         <v>100</v>
@@ -10331,10 +10331,10 @@
         <v>46043</v>
       </c>
       <c r="L208" s="0" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M208" s="0" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N208" s="0" t="n">
         <v>100</v>
@@ -10472,16 +10472,16 @@
         <v>46043</v>
       </c>
       <c r="L211" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M211" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N211" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>25</v>
       </c>
       <c r="O211" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>25</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10613,16 +10613,16 @@
         <v>46133</v>
       </c>
       <c r="L214" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M214" s="0" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N214" s="0" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="O214" s="0" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10754,16 +10754,16 @@
         <v>46133</v>
       </c>
       <c r="L217" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M217" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N217" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>25</v>
       </c>
       <c r="O217" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>25</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10895,16 +10895,16 @@
         <v>45859</v>
       </c>
       <c r="L220" s="0" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M220" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N220" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O220" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11036,16 +11036,16 @@
         <v>45859</v>
       </c>
       <c r="L223" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M223" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N223" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O223" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11177,16 +11177,16 @@
         <v>45951</v>
       </c>
       <c r="L226" s="0" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M226" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N226" s="0" t="n">
-        <v>71.4285714285714</v>
+        <v>50</v>
       </c>
       <c r="O226" s="0" t="n">
-        <v>71.4285714285714</v>
+        <v>50</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11318,16 +11318,16 @@
         <v>45951</v>
       </c>
       <c r="L229" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M229" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N229" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
       <c r="O229" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11459,16 +11459,16 @@
         <v>46043</v>
       </c>
       <c r="L232" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M232" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N232" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O232" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11600,16 +11600,16 @@
         <v>46043</v>
       </c>
       <c r="L235" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M235" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N235" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>50</v>
       </c>
       <c r="O235" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>50</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11741,10 +11741,10 @@
         <v>46133</v>
       </c>
       <c r="L238" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M238" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N238" s="0" t="n">
         <v>50</v>
@@ -11882,16 +11882,16 @@
         <v>46133</v>
       </c>
       <c r="L241" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M241" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N241" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>25</v>
       </c>
       <c r="O241" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>25</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12023,16 +12023,16 @@
         <v>45859</v>
       </c>
       <c r="L244" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M244" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N244" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="O244" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12164,16 +12164,16 @@
         <v>45859</v>
       </c>
       <c r="L247" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M247" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N247" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
       <c r="O247" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12305,16 +12305,16 @@
         <v>45951</v>
       </c>
       <c r="L250" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M250" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N250" s="0" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="O250" s="0" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12446,16 +12446,16 @@
         <v>45951</v>
       </c>
       <c r="L253" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M253" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N253" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="O253" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12587,16 +12587,16 @@
         <v>46043</v>
       </c>
       <c r="L256" s="0" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M256" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N256" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>100</v>
       </c>
       <c r="O256" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>100</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12728,16 +12728,16 @@
         <v>46043</v>
       </c>
       <c r="L259" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M259" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N259" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="O259" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12869,16 +12869,16 @@
         <v>46133</v>
       </c>
       <c r="L262" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M262" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N262" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O262" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13010,16 +13010,16 @@
         <v>46133</v>
       </c>
       <c r="L265" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M265" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N265" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O265" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13151,16 +13151,16 @@
         <v>45859</v>
       </c>
       <c r="L268" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M268" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N268" s="0" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="O268" s="0" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13292,7 +13292,7 @@
         <v>45859</v>
       </c>
       <c r="L271" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M271" s="0" t="n">
         <v>0</v>
@@ -13433,7 +13433,7 @@
         <v>45951</v>
       </c>
       <c r="L274" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M274" s="0" t="n">
         <v>0</v>
@@ -13574,16 +13574,16 @@
         <v>45951</v>
       </c>
       <c r="L277" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M277" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N277" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O277" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13715,16 +13715,16 @@
         <v>46043</v>
       </c>
       <c r="L280" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M280" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N280" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O280" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13856,16 +13856,16 @@
         <v>46043</v>
       </c>
       <c r="L283" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M283" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N283" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O283" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13997,16 +13997,16 @@
         <v>46133</v>
       </c>
       <c r="L286" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M286" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N286" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O286" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14138,7 +14138,7 @@
         <v>46133</v>
       </c>
       <c r="L289" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M289" s="0" t="n">
         <v>0</v>
@@ -14279,16 +14279,16 @@
         <v>45859</v>
       </c>
       <c r="L292" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M292" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N292" s="0" t="n">
-        <v>25</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O292" s="0" t="n">
-        <v>25</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14420,16 +14420,16 @@
         <v>45859</v>
       </c>
       <c r="L295" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M295" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N295" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
       <c r="O295" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14561,16 +14561,16 @@
         <v>45951</v>
       </c>
       <c r="L298" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M298" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N298" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O298" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14702,16 +14702,16 @@
         <v>45951</v>
       </c>
       <c r="L301" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M301" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N301" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O301" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14843,16 +14843,16 @@
         <v>46043</v>
       </c>
       <c r="L304" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M304" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N304" s="0" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="O304" s="0" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14984,16 +14984,16 @@
         <v>46043</v>
       </c>
       <c r="L307" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M307" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N307" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="O307" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15125,16 +15125,16 @@
         <v>46133</v>
       </c>
       <c r="L310" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M310" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N310" s="0" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O310" s="0" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15266,7 +15266,7 @@
         <v>46133</v>
       </c>
       <c r="L313" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M313" s="0" t="n">
         <v>0</v>
@@ -15407,16 +15407,16 @@
         <v>45859</v>
       </c>
       <c r="L316" s="0" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M316" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N316" s="0" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="O316" s="0" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15548,16 +15548,16 @@
         <v>45859</v>
       </c>
       <c r="L319" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M319" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N319" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O319" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15689,10 +15689,10 @@
         <v>45951</v>
       </c>
       <c r="L322" s="0" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M322" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N322" s="0" t="n">
         <v>50</v>
@@ -15830,16 +15830,16 @@
         <v>45951</v>
       </c>
       <c r="L325" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M325" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N325" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O325" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15971,16 +15971,16 @@
         <v>46043</v>
       </c>
       <c r="L328" s="0" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M328" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N328" s="0" t="n">
-        <v>55.5555555555556</v>
+        <v>0</v>
       </c>
       <c r="O328" s="0" t="n">
-        <v>55.5555555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16112,16 +16112,16 @@
         <v>46043</v>
       </c>
       <c r="L331" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M331" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N331" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
       <c r="O331" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16253,16 +16253,16 @@
         <v>46133</v>
       </c>
       <c r="L334" s="0" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M334" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N334" s="0" t="n">
-        <v>44.4444444444444</v>
+        <v>100</v>
       </c>
       <c r="O334" s="0" t="n">
-        <v>44.4444444444444</v>
+        <v>100</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16394,16 +16394,16 @@
         <v>46133</v>
       </c>
       <c r="L337" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M337" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N337" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="O337" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16535,16 +16535,16 @@
         <v>45859</v>
       </c>
       <c r="L340" s="0" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M340" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N340" s="0" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="O340" s="0" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16676,16 +16676,16 @@
         <v>45859</v>
       </c>
       <c r="L343" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M343" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N343" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O343" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16817,10 +16817,10 @@
         <v>45951</v>
       </c>
       <c r="L346" s="0" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M346" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N346" s="0" t="n">
         <v>33.3333333333333</v>
@@ -16961,13 +16961,13 @@
         <v>1</v>
       </c>
       <c r="M349" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N349" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O349" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17099,16 +17099,16 @@
         <v>46043</v>
       </c>
       <c r="L352" s="0" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M352" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N352" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>50</v>
       </c>
       <c r="O352" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>50</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17384,13 +17384,13 @@
         <v>4</v>
       </c>
       <c r="M358" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N358" s="0" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="O358" s="0" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17663,7 +17663,7 @@
         <v>45859</v>
       </c>
       <c r="L364" s="0" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M364" s="0" t="n">
         <v>0</v>
@@ -17804,16 +17804,16 @@
         <v>45859</v>
       </c>
       <c r="L367" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M367" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N367" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O367" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17945,16 +17945,16 @@
         <v>45951</v>
       </c>
       <c r="L370" s="0" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M370" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N370" s="0" t="n">
-        <v>7.69230769230769</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O370" s="0" t="n">
-        <v>7.69230769230769</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18086,16 +18086,16 @@
         <v>45951</v>
       </c>
       <c r="L373" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M373" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N373" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O373" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18227,16 +18227,16 @@
         <v>46043</v>
       </c>
       <c r="L376" s="0" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M376" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N376" s="0" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="O376" s="0" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18368,7 +18368,7 @@
         <v>46043</v>
       </c>
       <c r="L379" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M379" s="0" t="n">
         <v>0</v>
@@ -18509,16 +18509,16 @@
         <v>46133</v>
       </c>
       <c r="L382" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M382" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N382" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O382" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18650,7 +18650,7 @@
         <v>46133</v>
       </c>
       <c r="L385" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M385" s="0" t="n">
         <v>0</v>
@@ -18791,16 +18791,16 @@
         <v>45859</v>
       </c>
       <c r="L388" s="0" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M388" s="0" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N388" s="0" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O388" s="0" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18932,7 +18932,7 @@
         <v>45859</v>
       </c>
       <c r="L391" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M391" s="0" t="n">
         <v>0</v>
@@ -19073,16 +19073,16 @@
         <v>45951</v>
       </c>
       <c r="L394" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M394" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N394" s="0" t="n">
-        <v>37.5</v>
+        <v>14.2857142857143</v>
       </c>
       <c r="O394" s="0" t="n">
-        <v>37.5</v>
+        <v>14.2857142857143</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19214,10 +19214,10 @@
         <v>45951</v>
       </c>
       <c r="L397" s="0" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M397" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N397" s="0" t="n">
         <v>33.3333333333333</v>
@@ -19355,16 +19355,16 @@
         <v>46043</v>
       </c>
       <c r="L400" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M400" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N400" s="0" t="n">
-        <v>25</v>
+        <v>16.6666666666667</v>
       </c>
       <c r="O400" s="0" t="n">
-        <v>25</v>
+        <v>16.6666666666667</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19496,16 +19496,16 @@
         <v>46043</v>
       </c>
       <c r="L403" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M403" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N403" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O403" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19637,16 +19637,16 @@
         <v>46133</v>
       </c>
       <c r="L406" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M406" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N406" s="0" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O406" s="0" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19778,16 +19778,16 @@
         <v>46133</v>
       </c>
       <c r="L409" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M409" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N409" s="0" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O409" s="0" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19919,16 +19919,16 @@
         <v>45859</v>
       </c>
       <c r="L412" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M412" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N412" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="O412" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20342,16 +20342,16 @@
         <v>45951</v>
       </c>
       <c r="L421" s="0" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M421" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N421" s="0" t="n">
-        <v>83.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="O421" s="0" t="n">
-        <v>83.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20483,16 +20483,16 @@
         <v>46043</v>
       </c>
       <c r="L424" s="0" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M424" s="0" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N424" s="0" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="O424" s="0" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20624,16 +20624,16 @@
         <v>46043</v>
       </c>
       <c r="L427" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M427" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N427" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O427" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20765,16 +20765,16 @@
         <v>46133</v>
       </c>
       <c r="L430" s="0" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M430" s="0" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N430" s="0" t="n">
-        <v>77.7777777777778</v>
+        <v>0</v>
       </c>
       <c r="O430" s="0" t="n">
-        <v>77.7777777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20906,16 +20906,16 @@
         <v>46133</v>
       </c>
       <c r="L433" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M433" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N433" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O433" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21047,16 +21047,16 @@
         <v>45859</v>
       </c>
       <c r="L436" s="0" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M436" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N436" s="0" t="n">
-        <v>8.33333333333333</v>
+        <v>20</v>
       </c>
       <c r="O436" s="0" t="n">
-        <v>8.33333333333333</v>
+        <v>20</v>
       </c>
     </row>
     <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21188,7 +21188,7 @@
         <v>45859</v>
       </c>
       <c r="L439" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M439" s="0" t="n">
         <v>0</v>
@@ -21329,16 +21329,16 @@
         <v>45951</v>
       </c>
       <c r="L442" s="0" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M442" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N442" s="0" t="n">
-        <v>14.2857142857143</v>
+        <v>0</v>
       </c>
       <c r="O442" s="0" t="n">
-        <v>14.2857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21470,16 +21470,16 @@
         <v>45951</v>
       </c>
       <c r="L445" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M445" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N445" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O445" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21611,10 +21611,10 @@
         <v>46043</v>
       </c>
       <c r="L448" s="0" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M448" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N448" s="0" t="n">
         <v>33.3333333333333</v>
@@ -21752,16 +21752,16 @@
         <v>46043</v>
       </c>
       <c r="L451" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M451" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N451" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O451" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21893,16 +21893,16 @@
         <v>46133</v>
       </c>
       <c r="L454" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M454" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N454" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>50</v>
       </c>
       <c r="O454" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>50</v>
       </c>
     </row>
     <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22034,16 +22034,16 @@
         <v>46133</v>
       </c>
       <c r="L457" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M457" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N457" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="O457" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22175,16 +22175,16 @@
         <v>45859</v>
       </c>
       <c r="L460" s="0" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M460" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N460" s="0" t="n">
-        <v>27.2727272727273</v>
+        <v>25</v>
       </c>
       <c r="O460" s="0" t="n">
-        <v>27.2727272727273</v>
+        <v>25</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22316,16 +22316,16 @@
         <v>45859</v>
       </c>
       <c r="L463" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M463" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N463" s="0" t="n">
-        <v>60</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="O463" s="0" t="n">
-        <v>60</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22457,16 +22457,16 @@
         <v>45951</v>
       </c>
       <c r="L466" s="0" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M466" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N466" s="0" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O466" s="0" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22598,16 +22598,16 @@
         <v>45951</v>
       </c>
       <c r="L469" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M469" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N469" s="0" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="O469" s="0" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22739,16 +22739,16 @@
         <v>46043</v>
       </c>
       <c r="L472" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M472" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N472" s="0" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O472" s="0" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22880,16 +22880,16 @@
         <v>46043</v>
       </c>
       <c r="L475" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M475" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N475" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O475" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23021,16 +23021,16 @@
         <v>46133</v>
       </c>
       <c r="L478" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M478" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N478" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
       <c r="O478" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23162,10 +23162,10 @@
         <v>46133</v>
       </c>
       <c r="L481" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M481" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N481" s="0" t="n">
         <v>100</v>
@@ -23303,16 +23303,16 @@
         <v>45859</v>
       </c>
       <c r="L484" s="0" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M484" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N484" s="0" t="n">
-        <v>22.2222222222222</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O484" s="0" t="n">
-        <v>22.2222222222222</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23444,16 +23444,16 @@
         <v>45859</v>
       </c>
       <c r="L487" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M487" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N487" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="O487" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23585,16 +23585,16 @@
         <v>45951</v>
       </c>
       <c r="L490" s="0" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M490" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N490" s="0" t="n">
-        <v>44.4444444444444</v>
+        <v>50</v>
       </c>
       <c r="O490" s="0" t="n">
-        <v>44.4444444444444</v>
+        <v>50</v>
       </c>
     </row>
     <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23726,7 +23726,7 @@
         <v>45951</v>
       </c>
       <c r="L493" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M493" s="0" t="n">
         <v>0</v>
@@ -23867,16 +23867,16 @@
         <v>46043</v>
       </c>
       <c r="L496" s="0" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M496" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N496" s="0" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="O496" s="0" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24008,16 +24008,16 @@
         <v>46043</v>
       </c>
       <c r="L499" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M499" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N499" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O499" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24149,16 +24149,16 @@
         <v>46133</v>
       </c>
       <c r="L502" s="0" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M502" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N502" s="0" t="n">
-        <v>22.2222222222222</v>
+        <v>0</v>
       </c>
       <c r="O502" s="0" t="n">
-        <v>22.2222222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24290,16 +24290,16 @@
         <v>46133</v>
       </c>
       <c r="L505" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M505" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N505" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O505" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24431,7 +24431,7 @@
         <v>45859</v>
       </c>
       <c r="L508" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M508" s="0" t="n">
         <v>0</v>
@@ -24572,16 +24572,16 @@
         <v>45859</v>
       </c>
       <c r="L511" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M511" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N511" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O511" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24713,16 +24713,16 @@
         <v>45951</v>
       </c>
       <c r="L514" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M514" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N514" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O514" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24854,16 +24854,16 @@
         <v>45951</v>
       </c>
       <c r="L517" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M517" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N517" s="0" t="n">
-        <v>50</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="O517" s="0" t="n">
-        <v>50</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24995,16 +24995,16 @@
         <v>46043</v>
       </c>
       <c r="L520" s="0" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M520" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N520" s="0" t="n">
-        <v>50</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="O520" s="0" t="n">
-        <v>50</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25277,16 +25277,16 @@
         <v>46133</v>
       </c>
       <c r="L526" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M526" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N526" s="0" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O526" s="0" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25418,16 +25418,16 @@
         <v>46133</v>
       </c>
       <c r="L529" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M529" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N529" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O529" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25559,16 +25559,16 @@
         <v>45859</v>
       </c>
       <c r="L532" s="0" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M532" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N532" s="0" t="n">
-        <v>37.5</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="O532" s="0" t="n">
-        <v>37.5</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25700,16 +25700,16 @@
         <v>45859</v>
       </c>
       <c r="L535" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M535" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N535" s="0" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="O535" s="0" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25841,16 +25841,16 @@
         <v>45951</v>
       </c>
       <c r="L538" s="0" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M538" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N538" s="0" t="n">
-        <v>44.4444444444444</v>
+        <v>100</v>
       </c>
       <c r="O538" s="0" t="n">
-        <v>44.4444444444444</v>
+        <v>100</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25982,16 +25982,16 @@
         <v>45951</v>
       </c>
       <c r="L541" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M541" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N541" s="0" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="O541" s="0" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26123,16 +26123,16 @@
         <v>46043</v>
       </c>
       <c r="L544" s="0" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M544" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N544" s="0" t="n">
-        <v>55.5555555555556</v>
+        <v>100</v>
       </c>
       <c r="O544" s="0" t="n">
-        <v>55.5555555555556</v>
+        <v>100</v>
       </c>
     </row>
     <row r="545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26264,16 +26264,16 @@
         <v>46043</v>
       </c>
       <c r="L547" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M547" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N547" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O547" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26405,16 +26405,16 @@
         <v>46133</v>
       </c>
       <c r="L550" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M550" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N550" s="0" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="O550" s="0" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26546,10 +26546,10 @@
         <v>46133</v>
       </c>
       <c r="L553" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M553" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N553" s="0" t="n">
         <v>100</v>
@@ -26687,16 +26687,16 @@
         <v>45859</v>
       </c>
       <c r="L556" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M556" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N556" s="0" t="n">
-        <v>60</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="O556" s="0" t="n">
-        <v>60</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26828,7 +26828,7 @@
         <v>45859</v>
       </c>
       <c r="L559" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M559" s="0" t="n">
         <v>0</v>
@@ -26969,10 +26969,10 @@
         <v>45951</v>
       </c>
       <c r="L562" s="0" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M562" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N562" s="0" t="n">
         <v>33.3333333333333</v>
@@ -27110,16 +27110,16 @@
         <v>45951</v>
       </c>
       <c r="L565" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M565" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N565" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
       <c r="O565" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27251,16 +27251,16 @@
         <v>46043</v>
       </c>
       <c r="L568" s="0" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M568" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N568" s="0" t="n">
-        <v>14.2857142857143</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O568" s="0" t="n">
-        <v>14.2857142857143</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27392,16 +27392,16 @@
         <v>46043</v>
       </c>
       <c r="L571" s="0" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M571" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N571" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
       <c r="O571" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27533,16 +27533,16 @@
         <v>46133</v>
       </c>
       <c r="L574" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M574" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N574" s="0" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O574" s="0" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27674,16 +27674,16 @@
         <v>46133</v>
       </c>
       <c r="L577" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M577" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N577" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O577" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27815,16 +27815,16 @@
         <v>45859</v>
       </c>
       <c r="L580" s="0" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M580" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N580" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O580" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27956,16 +27956,16 @@
         <v>45859</v>
       </c>
       <c r="L583" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M583" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N583" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O583" s="0" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28097,16 +28097,16 @@
         <v>45951</v>
       </c>
       <c r="L586" s="0" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M586" s="0" t="n">
         <v>3</v>
       </c>
       <c r="N586" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
       <c r="O586" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28379,16 +28379,16 @@
         <v>46043</v>
       </c>
       <c r="L592" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M592" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N592" s="0" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="O592" s="0" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="593" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28520,16 +28520,16 @@
         <v>46043</v>
       </c>
       <c r="L595" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M595" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N595" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
       <c r="O595" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28664,13 +28664,13 @@
         <v>4</v>
       </c>
       <c r="M598" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N598" s="0" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="O598" s="0" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="599" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28802,16 +28802,16 @@
         <v>46133</v>
       </c>
       <c r="L601" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M601" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N601" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O601" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28943,16 +28943,16 @@
         <v>45859</v>
       </c>
       <c r="L604" s="0" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M604" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N604" s="0" t="n">
-        <v>42.8571428571429</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="O604" s="0" t="n">
-        <v>42.8571428571429</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="605" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29084,16 +29084,16 @@
         <v>45859</v>
       </c>
       <c r="L607" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M607" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N607" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
       <c r="O607" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29225,16 +29225,16 @@
         <v>45951</v>
       </c>
       <c r="L610" s="0" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M610" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N610" s="0" t="n">
-        <v>44.4444444444444</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="O610" s="0" t="n">
-        <v>44.4444444444444</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29366,16 +29366,16 @@
         <v>45951</v>
       </c>
       <c r="L613" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M613" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N613" s="0" t="n">
-        <v>0</v>
+        <v>16.6666666666667</v>
       </c>
       <c r="O613" s="0" t="n">
-        <v>0</v>
+        <v>16.6666666666667</v>
       </c>
     </row>
     <row r="614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29507,16 +29507,16 @@
         <v>46043</v>
       </c>
       <c r="L616" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M616" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N616" s="0" t="n">
-        <v>22.2222222222222</v>
+        <v>25</v>
       </c>
       <c r="O616" s="0" t="n">
-        <v>22.2222222222222</v>
+        <v>25</v>
       </c>
     </row>
     <row r="617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29789,16 +29789,16 @@
         <v>46133</v>
       </c>
       <c r="L622" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M622" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N622" s="0" t="n">
-        <v>0</v>
+        <v>16.6666666666667</v>
       </c>
       <c r="O622" s="0" t="n">
-        <v>0</v>
+        <v>16.6666666666667</v>
       </c>
     </row>
     <row r="623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29930,16 +29930,16 @@
         <v>46133</v>
       </c>
       <c r="L625" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M625" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N625" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O625" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30071,16 +30071,16 @@
         <v>45859</v>
       </c>
       <c r="L628" s="0" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M628" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N628" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O628" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30212,16 +30212,16 @@
         <v>45859</v>
       </c>
       <c r="L631" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M631" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N631" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O631" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30353,16 +30353,16 @@
         <v>45951</v>
       </c>
       <c r="L634" s="0" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M634" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N634" s="0" t="n">
-        <v>42.8571428571429</v>
+        <v>20</v>
       </c>
       <c r="O634" s="0" t="n">
-        <v>42.8571428571429</v>
+        <v>20</v>
       </c>
     </row>
     <row r="635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30635,16 +30635,16 @@
         <v>46043</v>
       </c>
       <c r="L640" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M640" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N640" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O640" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="641" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31058,16 +31058,16 @@
         <v>46133</v>
       </c>
       <c r="L649" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M649" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N649" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="O649" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="650" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31199,16 +31199,16 @@
         <v>45859</v>
       </c>
       <c r="L652" s="0" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M652" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N652" s="0" t="n">
-        <v>71.4285714285714</v>
+        <v>60</v>
       </c>
       <c r="O652" s="0" t="n">
-        <v>71.4285714285714</v>
+        <v>60</v>
       </c>
     </row>
     <row r="653" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31340,16 +31340,16 @@
         <v>45859</v>
       </c>
       <c r="L655" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M655" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N655" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O655" s="0" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="656" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31481,16 +31481,16 @@
         <v>45951</v>
       </c>
       <c r="L658" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M658" s="0" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N658" s="0" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="O658" s="0" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="659" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31622,16 +31622,16 @@
         <v>45951</v>
       </c>
       <c r="L661" s="0" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M661" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N661" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O661" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="662" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31763,16 +31763,16 @@
         <v>46043</v>
       </c>
       <c r="L664" s="0" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M664" s="0" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N664" s="0" t="n">
-        <v>72.7272727272727</v>
+        <v>50</v>
       </c>
       <c r="O664" s="0" t="n">
-        <v>72.7272727272727</v>
+        <v>50</v>
       </c>
     </row>
     <row r="665" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31904,16 +31904,16 @@
         <v>46043</v>
       </c>
       <c r="L667" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M667" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N667" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O667" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="668" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32045,16 +32045,16 @@
         <v>46133</v>
       </c>
       <c r="L670" s="0" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M670" s="0" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N670" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O670" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="671" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32186,16 +32186,16 @@
         <v>46133</v>
       </c>
       <c r="L673" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M673" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N673" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O673" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="674" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32327,16 +32327,16 @@
         <v>45859</v>
       </c>
       <c r="L676" s="0" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M676" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N676" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>0</v>
       </c>
       <c r="O676" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="677" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32468,16 +32468,16 @@
         <v>45859</v>
       </c>
       <c r="L679" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M679" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N679" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O679" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="680" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32609,16 +32609,16 @@
         <v>45951</v>
       </c>
       <c r="L682" s="0" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M682" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N682" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O682" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="683" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32753,13 +32753,13 @@
         <v>4</v>
       </c>
       <c r="M685" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N685" s="0" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O685" s="0" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="686" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32891,16 +32891,16 @@
         <v>46043</v>
       </c>
       <c r="L688" s="0" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M688" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N688" s="0" t="n">
-        <v>28.5714285714286</v>
+        <v>25</v>
       </c>
       <c r="O688" s="0" t="n">
-        <v>28.5714285714286</v>
+        <v>25</v>
       </c>
     </row>
     <row r="689" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33032,16 +33032,16 @@
         <v>46043</v>
       </c>
       <c r="L691" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M691" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N691" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O691" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="692" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33173,16 +33173,16 @@
         <v>46133</v>
       </c>
       <c r="L694" s="0" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M694" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N694" s="0" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="O694" s="0" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="695" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33314,10 +33314,10 @@
         <v>46133</v>
       </c>
       <c r="L697" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M697" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N697" s="0" t="n">
         <v>100</v>
@@ -33455,16 +33455,16 @@
         <v>45859</v>
       </c>
       <c r="L700" s="0" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M700" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N700" s="0" t="n">
-        <v>42.8571428571429</v>
+        <v>80</v>
       </c>
       <c r="O700" s="0" t="n">
-        <v>42.8571428571429</v>
+        <v>80</v>
       </c>
     </row>
     <row r="701" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33596,16 +33596,16 @@
         <v>45859</v>
       </c>
       <c r="L703" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M703" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N703" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O703" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="704" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33737,10 +33737,10 @@
         <v>45951</v>
       </c>
       <c r="L706" s="0" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M706" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N706" s="0" t="n">
         <v>50</v>
@@ -33881,13 +33881,13 @@
         <v>3</v>
       </c>
       <c r="M709" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N709" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="O709" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="710" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34019,16 +34019,16 @@
         <v>46043</v>
       </c>
       <c r="L712" s="0" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M712" s="0" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N712" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O712" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="713" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34163,13 +34163,13 @@
         <v>3</v>
       </c>
       <c r="M715" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N715" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
       <c r="O715" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="716" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34304,13 +34304,13 @@
         <v>7</v>
       </c>
       <c r="M718" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N718" s="0" t="n">
-        <v>28.5714285714286</v>
+        <v>42.8571428571429</v>
       </c>
       <c r="O718" s="0" t="n">
-        <v>28.5714285714286</v>
+        <v>42.8571428571429</v>
       </c>
     </row>
     <row r="719" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34442,10 +34442,10 @@
         <v>46133</v>
       </c>
       <c r="L721" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M721" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N721" s="0" t="n">
         <v>100</v>
@@ -34583,16 +34583,16 @@
         <v>45859</v>
       </c>
       <c r="L724" s="0" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M724" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N724" s="0" t="n">
-        <v>55.5555555555556</v>
+        <v>100</v>
       </c>
       <c r="O724" s="0" t="n">
-        <v>55.5555555555556</v>
+        <v>100</v>
       </c>
     </row>
     <row r="725" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34724,7 +34724,7 @@
         <v>45859</v>
       </c>
       <c r="L727" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M727" s="0" t="n">
         <v>0</v>
@@ -34865,16 +34865,16 @@
         <v>45951</v>
       </c>
       <c r="L730" s="0" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M730" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N730" s="0" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="O730" s="0" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="731" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35006,16 +35006,16 @@
         <v>45951</v>
       </c>
       <c r="L733" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M733" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N733" s="0" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="O733" s="0" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="734" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35147,16 +35147,16 @@
         <v>46043</v>
       </c>
       <c r="L736" s="0" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M736" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N736" s="0" t="n">
-        <v>14.2857142857143</v>
+        <v>20</v>
       </c>
       <c r="O736" s="0" t="n">
-        <v>14.2857142857143</v>
+        <v>20</v>
       </c>
     </row>
     <row r="737" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35429,16 +35429,16 @@
         <v>46133</v>
       </c>
       <c r="L742" s="0" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M742" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N742" s="0" t="n">
-        <v>50</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O742" s="0" t="n">
-        <v>50</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="743" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35570,7 +35570,7 @@
         <v>46133</v>
       </c>
       <c r="L745" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M745" s="0" t="n">
         <v>0</v>
@@ -35711,16 +35711,16 @@
         <v>45859</v>
       </c>
       <c r="L748" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M748" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N748" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O748" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="749" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35852,16 +35852,16 @@
         <v>45859</v>
       </c>
       <c r="L751" s="0" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M751" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N751" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O751" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="752" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35993,16 +35993,16 @@
         <v>45951</v>
       </c>
       <c r="L754" s="0" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M754" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N754" s="0" t="n">
-        <v>71.4285714285714</v>
+        <v>100</v>
       </c>
       <c r="O754" s="0" t="n">
-        <v>71.4285714285714</v>
+        <v>100</v>
       </c>
     </row>
     <row r="755" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36134,10 +36134,10 @@
         <v>45951</v>
       </c>
       <c r="L757" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M757" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N757" s="0" t="n">
         <v>100</v>
@@ -36275,16 +36275,16 @@
         <v>46043</v>
       </c>
       <c r="L760" s="0" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M760" s="0" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N760" s="0" t="n">
-        <v>77.7777777777778</v>
+        <v>100</v>
       </c>
       <c r="O760" s="0" t="n">
-        <v>77.7777777777778</v>
+        <v>100</v>
       </c>
     </row>
     <row r="761" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36416,16 +36416,16 @@
         <v>46043</v>
       </c>
       <c r="L763" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M763" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N763" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="O763" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="764" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36557,16 +36557,16 @@
         <v>46133</v>
       </c>
       <c r="L766" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M766" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N766" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="O766" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="767" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36839,16 +36839,16 @@
         <v>45859</v>
       </c>
       <c r="L772" s="0" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M772" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N772" s="0" t="n">
-        <v>0</v>
+        <v>42.8571428571429</v>
       </c>
       <c r="O772" s="0" t="n">
-        <v>0</v>
+        <v>42.8571428571429</v>
       </c>
     </row>
     <row r="773" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36983,13 +36983,13 @@
         <v>2</v>
       </c>
       <c r="M775" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N775" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O775" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="776" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37121,16 +37121,16 @@
         <v>45951</v>
       </c>
       <c r="L778" s="0" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M778" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N778" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>55.5555555555556</v>
       </c>
       <c r="O778" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>55.5555555555556</v>
       </c>
     </row>
     <row r="779" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37262,7 +37262,7 @@
         <v>45951</v>
       </c>
       <c r="L781" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M781" s="0" t="n">
         <v>0</v>
@@ -37403,16 +37403,16 @@
         <v>46043</v>
       </c>
       <c r="L784" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M784" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N784" s="0" t="n">
-        <v>25</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O784" s="0" t="n">
-        <v>25</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="785" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37544,16 +37544,16 @@
         <v>46043</v>
       </c>
       <c r="L787" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M787" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N787" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>50</v>
       </c>
       <c r="O787" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>50</v>
       </c>
     </row>
     <row r="788" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37685,16 +37685,16 @@
         <v>46133</v>
       </c>
       <c r="L790" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M790" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N790" s="0" t="n">
-        <v>28.5714285714286</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O790" s="0" t="n">
-        <v>28.5714285714286</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="791" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37826,16 +37826,16 @@
         <v>46133</v>
       </c>
       <c r="L793" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M793" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N793" s="0" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="O793" s="0" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="794" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37967,16 +37967,16 @@
         <v>45859</v>
       </c>
       <c r="L796" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M796" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N796" s="0" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O796" s="0" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="797" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38108,16 +38108,16 @@
         <v>45859</v>
       </c>
       <c r="L799" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M799" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N799" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O799" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="800" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38249,16 +38249,16 @@
         <v>45951</v>
       </c>
       <c r="L802" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M802" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N802" s="0" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O802" s="0" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="803" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38390,16 +38390,16 @@
         <v>45951</v>
       </c>
       <c r="L805" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M805" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N805" s="0" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="O805" s="0" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="806" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38531,16 +38531,16 @@
         <v>46043</v>
       </c>
       <c r="L808" s="0" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M808" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N808" s="0" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="O808" s="0" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="809" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38672,16 +38672,16 @@
         <v>46043</v>
       </c>
       <c r="L811" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M811" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N811" s="0" t="n">
-        <v>60</v>
+        <v>66.6666666666667</v>
       </c>
       <c r="O811" s="0" t="n">
-        <v>60</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="812" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38813,16 +38813,16 @@
         <v>46133</v>
       </c>
       <c r="L814" s="0" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M814" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N814" s="0" t="n">
-        <v>36.3636363636364</v>
+        <v>60</v>
       </c>
       <c r="O814" s="0" t="n">
-        <v>36.3636363636364</v>
+        <v>60</v>
       </c>
     </row>
     <row r="815" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38954,16 +38954,16 @@
         <v>46133</v>
       </c>
       <c r="L817" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M817" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N817" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="O817" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="818" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39098,13 +39098,13 @@
         <v>4</v>
       </c>
       <c r="M820" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N820" s="0" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="O820" s="0" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="821" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39236,16 +39236,16 @@
         <v>45859</v>
       </c>
       <c r="L823" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M823" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N823" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="O823" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="824" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39377,16 +39377,16 @@
         <v>45951</v>
       </c>
       <c r="L826" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M826" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N826" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O826" s="0" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="827" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39518,16 +39518,16 @@
         <v>45951</v>
       </c>
       <c r="L829" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M829" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N829" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O829" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="830" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39662,13 +39662,13 @@
         <v>7</v>
       </c>
       <c r="M832" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N832" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>42.8571428571429</v>
       </c>
       <c r="O832" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>42.8571428571429</v>
       </c>
     </row>
     <row r="833" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39800,16 +39800,16 @@
         <v>46043</v>
       </c>
       <c r="L835" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M835" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N835" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O835" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="836" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39944,13 +39944,13 @@
         <v>6</v>
       </c>
       <c r="M838" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N838" s="0" t="n">
-        <v>83.3333333333333</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O838" s="0" t="n">
-        <v>83.3333333333333</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="839" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40223,10 +40223,10 @@
         <v>45859</v>
       </c>
       <c r="L844" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M844" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N844" s="0" t="n">
         <v>100</v>
@@ -40364,16 +40364,16 @@
         <v>45859</v>
       </c>
       <c r="L847" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M847" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N847" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="O847" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="848" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40505,16 +40505,16 @@
         <v>45951</v>
       </c>
       <c r="L850" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M850" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N850" s="0" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O850" s="0" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="851" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40646,7 +40646,7 @@
         <v>45951</v>
       </c>
       <c r="L853" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M853" s="0" t="n">
         <v>0</v>
@@ -40787,16 +40787,16 @@
         <v>46043</v>
       </c>
       <c r="L856" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M856" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N856" s="0" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O856" s="0" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="857" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40928,16 +40928,16 @@
         <v>46043</v>
       </c>
       <c r="L859" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M859" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N859" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O859" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="860" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41069,16 +41069,16 @@
         <v>46133</v>
       </c>
       <c r="L862" s="0" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M862" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N862" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
       <c r="O862" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="863" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41210,7 +41210,7 @@
         <v>46133</v>
       </c>
       <c r="L865" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M865" s="0" t="n">
         <v>0</v>
@@ -41351,16 +41351,16 @@
         <v>45859</v>
       </c>
       <c r="L868" s="0" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M868" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N868" s="0" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="O868" s="0" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="869" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41492,16 +41492,16 @@
         <v>45859</v>
       </c>
       <c r="L871" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M871" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N871" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O871" s="0" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="872" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41633,16 +41633,16 @@
         <v>45951</v>
       </c>
       <c r="L874" s="0" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M874" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N874" s="0" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="O874" s="0" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="875" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41774,16 +41774,16 @@
         <v>45951</v>
       </c>
       <c r="L877" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M877" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N877" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O877" s="0" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="878" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41915,16 +41915,16 @@
         <v>46043</v>
       </c>
       <c r="L880" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M880" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N880" s="0" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="O880" s="0" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="881" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42056,16 +42056,16 @@
         <v>46043</v>
       </c>
       <c r="L883" s="0" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M883" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N883" s="0" t="n">
-        <v>16.6666666666667</v>
+        <v>50</v>
       </c>
       <c r="O883" s="0" t="n">
-        <v>16.6666666666667</v>
+        <v>50</v>
       </c>
     </row>
     <row r="884" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42197,16 +42197,16 @@
         <v>46133</v>
       </c>
       <c r="L886" s="0" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M886" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N886" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>57.1428571428571</v>
       </c>
       <c r="O886" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>57.1428571428571</v>
       </c>
     </row>
     <row r="887" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42338,7 +42338,7 @@
         <v>46133</v>
       </c>
       <c r="L889" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M889" s="0" t="n">
         <v>0</v>
@@ -42479,16 +42479,16 @@
         <v>45859</v>
       </c>
       <c r="L892" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M892" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N892" s="0" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="O892" s="0" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="893" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42620,16 +42620,16 @@
         <v>45859</v>
       </c>
       <c r="L895" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M895" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N895" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O895" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="896" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42761,16 +42761,16 @@
         <v>45951</v>
       </c>
       <c r="L898" s="0" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M898" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N898" s="0" t="n">
-        <v>83.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="O898" s="0" t="n">
-        <v>83.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="899" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42905,13 +42905,13 @@
         <v>3</v>
       </c>
       <c r="M901" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N901" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O901" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="902" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43043,16 +43043,16 @@
         <v>46043</v>
       </c>
       <c r="L904" s="0" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M904" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N904" s="0" t="n">
-        <v>71.4285714285714</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="O904" s="0" t="n">
-        <v>71.4285714285714</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="905" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43184,16 +43184,16 @@
         <v>46043</v>
       </c>
       <c r="L907" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M907" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N907" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
       <c r="O907" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>50</v>
       </c>
     </row>
     <row r="908" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43325,16 +43325,16 @@
         <v>46133</v>
       </c>
       <c r="L910" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M910" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N910" s="0" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O910" s="0" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="911" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43466,16 +43466,16 @@
         <v>46133</v>
       </c>
       <c r="L913" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M913" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N913" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="O913" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="914" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43607,16 +43607,16 @@
         <v>45859</v>
       </c>
       <c r="L916" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M916" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N916" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
       <c r="O916" s="0" t="n">
-        <v>33.3333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="917" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43748,16 +43748,16 @@
         <v>45859</v>
       </c>
       <c r="L919" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M919" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N919" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O919" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="920" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43889,16 +43889,16 @@
         <v>45951</v>
       </c>
       <c r="L922" s="0" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M922" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N922" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O922" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="923" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44030,7 +44030,7 @@
         <v>45951</v>
       </c>
       <c r="L925" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M925" s="0" t="n">
         <v>0</v>
@@ -44171,16 +44171,16 @@
         <v>46043</v>
       </c>
       <c r="L928" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M928" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N928" s="0" t="n">
-        <v>16.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O928" s="0" t="n">
-        <v>16.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="929" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44453,7 +44453,7 @@
         <v>46133</v>
       </c>
       <c r="L934" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M934" s="0" t="n">
         <v>0</v>
@@ -44594,7 +44594,7 @@
         <v>46133</v>
       </c>
       <c r="L937" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M937" s="0" t="n">
         <v>0</v>
@@ -44735,16 +44735,16 @@
         <v>45859</v>
       </c>
       <c r="L940" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M940" s="0" t="n">
         <v>4</v>
       </c>
       <c r="N940" s="0" t="n">
-        <v>50</v>
+        <v>57.1428571428571</v>
       </c>
       <c r="O940" s="0" t="n">
-        <v>50</v>
+        <v>57.1428571428571</v>
       </c>
     </row>
     <row r="941" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44876,16 +44876,16 @@
         <v>45859</v>
       </c>
       <c r="L943" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M943" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N943" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="O943" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="944" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45017,10 +45017,10 @@
         <v>45951</v>
       </c>
       <c r="L946" s="0" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M946" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N946" s="0" t="n">
         <v>50</v>
@@ -45158,16 +45158,16 @@
         <v>45951</v>
       </c>
       <c r="L949" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M949" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N949" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O949" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="950" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45299,16 +45299,16 @@
         <v>46043</v>
       </c>
       <c r="L952" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M952" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N952" s="0" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O952" s="0" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="953" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45440,16 +45440,16 @@
         <v>46043</v>
       </c>
       <c r="L955" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M955" s="0" t="n">
         <v>1</v>
       </c>
       <c r="N955" s="0" t="n">
-        <v>16.6666666666667</v>
+        <v>100</v>
       </c>
       <c r="O955" s="0" t="n">
-        <v>16.6666666666667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="956" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45581,16 +45581,16 @@
         <v>46133</v>
       </c>
       <c r="L958" s="0" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M958" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N958" s="0" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O958" s="0" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="959" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
